--- a/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位生命+25%</t>
+          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻击+25%</t>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻速+18%</t>
+          <t>备选：原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、Arquebus；最直接一条：火药单位-20%</t>
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、Arquebus；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 Arquebus；最直接一条：城堡时代可用化学/火枪手</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻击+25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻速+18%</t>
+          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、Arquebus；最直接一条：火药单位-20%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、Arquebus；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3）；火枪手科技树 9/11。缺：攻城工程技师、Arquebus</t>
+          <t>原生条目 4 条（强 3）；火枪手科技树 9/11。缺：攻城工程技师、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；火枪手科技树 10/11。缺：Arquebus</t>
+          <t>原生条目 2 条（强 2）；火枪手科技树 10/11。缺：火绳枪</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；火枪手科技树 9/11。缺：攻城工程技师、Arquebus</t>
+          <t>原生条目 1 条（强 1）；火枪手科技树 9/11。缺：攻城工程技师、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；火枪手科技树 9/11。缺：攻城工程技师、Arquebus</t>
+          <t>原生条目 2 条（强 2）；火枪手科技树 9/11。缺：攻城工程技师、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；火枪手科技树 8/11。缺：攻城工程技师、工兵、Arquebus</t>
+          <t>原生条目 2 条（强 2）；火枪手科技树 8/11。缺：攻城工程技师、工兵、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；火枪手科技树 7/11。缺：炮塔、工兵、建筑学、Arquebus</t>
+          <t>原生条目 2 条（强 2）；火枪手科技树 7/11。缺：炮塔、工兵、建筑学、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位生命+25%</t>
+          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 Arquebus；最直接一条：城堡时代可用化学/火枪手</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻击+25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、Arquebus；最直接一条：火药单位攻速+18%</t>
+          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、Arquebus；最直接一条：火药单位-20%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、Arquebus；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·火枪手本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与火枪手流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -20,10 +20,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·火枪手本体强化'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·火枪手本体强化'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·火枪手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与火枪手流无关·可跳过'!$A$1:$D$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与火枪手流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$8</definedName>
@@ -571,12 +571,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>火药单位生命+25%；火药单位训练速度 +25%</t>
+          <t>火药单位生命+25%；火炮术（炮塔/手推炮/炮舰射程+2）；火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 11/11（无缺项）；最直接一条：火绳枪（火药单位攻击移动目标准确度更高）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；火枪手科技树 11/11（无缺项）；最直接一条：火绳枪（火药单位攻击移动目标准确度更高）</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>火药单位攻速+18%</t>
+          <t>火药单位攻速+18%；炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -975,71 +975,71 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>射程提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>火药单位训练速度 +25%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>提升命中率与对移动目标的准确度，减少空枪</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>城堡时代可用化学/火枪手</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1056,44 +1056,44 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>城堡时代可用化学/火枪手</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
           <t>大车阵战术（火药单位移速+10%）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>火药单位攻击+25%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>火药单位攻速+18%</t>
+          <t>火药单位攻击+25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1132,26 +1132,26 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
+          <t>火药单位攻速+18%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>火药单位近战护甲+1/远程护甲+1</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
         </is>
       </c>
     </row>
@@ -1186,27 +1186,108 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>火药单位-20%</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>印度斯坦</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>火药单位近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>印度火铳（火枪手射程+2）</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>射程提升</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1218,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1256,19 +1337,19 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>火药单位-20%</t>
+          <t>化学免费，火药技术成本-50%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1278,12 +1359,39 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>免费获得，等于直接省下这笔支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2632,7 +2740,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；火枪手科技树 11/11。科技树无缺项</t>
+          <t>原生条目 2 条（强 1）；火枪手科技树 11/11。科技树无缺项</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2946,12 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>火药单位生命+25%；火药单位训练速度 +25%</t>
+          <t>火药单位生命+25%；火炮术（炮塔/手推炮/炮舰射程+2）；火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2981,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 11/11（无缺项）；最直接一条：火绳枪（火药单位攻击移动目标准确度更高）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；火枪手科技树 11/11（无缺项）；最直接一条：火绳枪（火药单位攻击移动目标准确度更高）</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3011,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 10/11；缺 火绳枪；最直接一条：城堡时代可用化学/火枪手</t>
         </is>
       </c>
     </row>
@@ -2933,7 +3041,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻击+25%</t>
         </is>
       </c>
     </row>
@@ -2958,12 +3066,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>火药单位攻速+18%</t>
+          <t>火药单位攻速+18%；炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位攻速+18%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3101,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 8/11；缺 攻城工程技师、工兵、火绳枪；最直接一条：火药单位-20%</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3131,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；火枪手科技树 7/11；缺 炮塔、工兵、建筑学、火绳枪；最直接一条：火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4821,101 +4929,141 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>① 只看直接作用于火枪手本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与火枪手流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
+          <t>直接加强火枪手本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（火药单位（火枪手/手推炮/炮舰等））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="10" t="inlineStr"/>
-      <c r="B16" s="10" t="inlineStr"/>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A18" s="10" t="inlineStr"/>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与火枪手流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="10" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="10" t="inlineStr"/>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A22" s="10" t="inlineStr"/>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 火枪手流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·火枪手本体强化'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·火枪手本体强化'!$A$1:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·火枪手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与火枪手流无关·可跳过'!$A$1:$D$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与火枪手流无关·可跳过'!$1:$1</definedName>
@@ -571,12 +571,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>火药单位生命+25%；火炮术（炮塔/手推炮/炮舰射程+2）；火药单位训练速度 +25%</t>
+          <t>火药单位生命+25%；火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>火药单位-20%；烟火之术（火枪手穿透伤害+15%且更准）</t>
+          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>火药单位近战护甲+1/远程护甲+1；印度火铳（火枪手射程+2）</t>
+          <t>印度火铳（火枪手射程+2）；火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -975,71 +975,71 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>射程提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>火药单位训练速度 +25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>训练速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>火绳枪（火药单位攻击移动目标准确度更高）</t>
+          <t>城堡时代可用化学/火枪手</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>提升命中率与对移动目标的准确度，减少空枪</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -1056,44 +1056,44 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可用化学/火枪手</t>
+          <t>大车阵战术（火药单位移速+10%）</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>火药单位攻击+25%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>提前解锁，抢一个时代的节奏</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>大车阵战术（火药单位移速+10%）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>火药单位攻击+25%</t>
+          <t>火药单位攻速+18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1120,11 +1120,11 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>火药单位攻速+18%</t>
+          <t>炮舰攻击移动目标更准</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1147,11 +1147,11 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>提升命中率与对移动目标的准确度，减少空枪</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>炮舰攻击移动目标更准</t>
+          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>提升命中率与对移动目标的准确度，减少空枪</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>火药单位-20%</t>
+          <t>火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
+          <t>印度火铳（火枪手射程+2）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1228,66 +1228,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>火药单位近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>印度火铳（火枪手射程+2）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
           <t>射程提升</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1299,7 +1245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1390,8 +1336,35 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>火药单位-20%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2710,12 +2683,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>火药单位生命+25%；火炮术（炮塔/手推炮/炮舰射程+2）</t>
+          <t>火药单位生命+25%；火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 3）；火枪手科技树 9/11。缺：攻城工程技师、火绳枪</t>
+          <t>原生条目 3 条（强 2）；火枪手科技树 9/11。缺：攻城工程技师、火绳枪</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2919,12 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>火药单位生命+25%；火炮术（炮塔/手推炮/炮舰射程+2）；火药单位训练速度 +25%</t>
+          <t>火药单位生命+25%；火药单位训练速度 +25%</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 2）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；火枪手科技树 9/11；缺 攻城工程技师、火绳枪；最直接一条：火药单位生命+25%</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3069,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>火药单位-20%；烟火之术（火枪手穿透伤害+15%且更准）</t>
+          <t>烟火之术（火枪手穿透伤害+15%且更准）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -3126,7 +3099,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>火药单位近战护甲+1/远程护甲+1；印度火铳（火枪手射程+2）</t>
+          <t>印度火铳（火枪手射程+2）；火药单位近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
